--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2346,6 +2346,41 @@
         <v>11823.998</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>39.91452504975582</v>
+      </c>
+      <c r="F60" t="n">
+        <v>18.96887968290206</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sep 14, 2026</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2026-09-16 18:58:00</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>11175.547</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2381,6 +2381,41 @@
         <v>11175.547</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>40.41982857353539</v>
+      </c>
+      <c r="F61" t="n">
+        <v>19.64186556960535</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:01:08</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>11599.492</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2416,76 @@
         <v>11599.492</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>41.72019516349453</v>
+      </c>
+      <c r="F62" t="n">
+        <v>20.12742720701993</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:41:09</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>11921.686</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>47.15959384904053</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.6205658126264</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sep 22, 2026</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:03:23</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>12534.274</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2486,6 +2486,76 @@
         <v>12534.274</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>47.20187466514123</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.75829039130397</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sep 24, 2026</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2026-09-25 23:59:55</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>12643.115</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>47.22938299444659</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.79594926387709</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sep 24, 2026</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:42:23</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>12668.929</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2556,6 +2556,59 @@
         <v>12668.929</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>42.36002399284372</v>
+      </c>
+      <c r="F67" t="n">
+        <v>19.28584533120963</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Oct 08, 2026</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2026-10-10 01:03:06</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>12530.396</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>42.36002399284372</v>
+        <v>42.3275361167227</v>
       </c>
       <c r="F67" t="n">
-        <v>19.28584533120963</v>
+        <v>19.27004389941623</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-10 01:03:06</t>
+          <t>2026-10-10 01:07:42</t>
         </is>
       </c>
       <c r="S67" t="n">
-        <v>12530.396</v>
+        <v>12524.354</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2584,7 +2584,7 @@
         <v>42.3275361167227</v>
       </c>
       <c r="F67" t="n">
-        <v>19.27004389941623</v>
+        <v>19.27004389941624</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2607,6 +2607,41 @@
       </c>
       <c r="S67" t="n">
         <v>12524.354</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>40.32706176853382</v>
+      </c>
+      <c r="F68" t="n">
+        <v>17.66750375164328</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Oct 14, 2026</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2026-10-15 23:43:07</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>11440.8</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>40.32706176853382</v>
+        <v>40.33092849088234</v>
       </c>
       <c r="F68" t="n">
-        <v>17.66750375164328</v>
+        <v>17.67588160730269</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2637,11 +2637,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-15 23:43:07</t>
+          <t>2026-10-15 23:51:47</t>
         </is>
       </c>
       <c r="S68" t="n">
-        <v>11440.8</v>
+        <v>11441.429</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>40.33092849088234</v>
+        <v>40.34321032279398</v>
       </c>
       <c r="F68" t="n">
-        <v>17.67588160730269</v>
+        <v>17.67994407819056</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2637,11 +2637,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-15 23:51:47</t>
+          <t>2026-10-15 23:55:11</t>
         </is>
       </c>
       <c r="S68" t="n">
-        <v>11441.429</v>
+        <v>11447.232</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:S69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2644,6 +2644,41 @@
         <v>11447.232</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>40.48087808412814</v>
+      </c>
+      <c r="F69" t="n">
+        <v>17.73758674062233</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Oct 14, 2026</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:03:08</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>11484.216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -2651,14 +2651,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>40.48087808412814</v>
+        <v>38.52252777730948</v>
       </c>
       <c r="F69" t="n">
-        <v>17.73758674062233</v>
+        <v>17.73938482029203</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oct 14, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-16 00:03:08</t>
+          <t>2026-10-16 20:12:26</t>
         </is>
       </c>
       <c r="S69" t="n">
-        <v>11484.216</v>
+        <v>11581.215</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S69"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2679,6 +2679,41 @@
         <v>11581.215</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>37.42806945912579</v>
+      </c>
+      <c r="F70" t="n">
+        <v>17.14374117926342</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Oct 19, 2026</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2026-10-21 16:17:53</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>11283.812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
